--- a/excel_files/lots.xlsx
+++ b/excel_files/lots.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>Ссылка</t>
   </si>
@@ -28,97 +28,49 @@
     <t>Лот</t>
   </si>
   <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14934791</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14934356</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14934200</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14933265</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14932608</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14931929</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14930947</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14930598</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14930206</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14930147</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14930087</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14929636</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14929429</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14928924</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14928398</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14927770</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14927324</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14926630</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14926479</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14924913</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14924838</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14923759</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14921480</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14921209</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14921059</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14920638</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14916286</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14917742</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14913904</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14910704</t>
-  </si>
-  <si>
-    <t>https://www.goszakup.gov.kz/ru/announce/index/14903361</t>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15169476</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15169407</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15169260</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15168913</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15165855</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15163633</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15163873</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15163518</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15163400</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15157634</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15158874</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15156017</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15155966</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15151430</t>
+  </si>
+  <si>
+    <t>https://www.goszakup.gov.kz/ru/announce/index/15147756</t>
   </si>
   <si>
     <t>Запрос ценовых предложений</t>
@@ -127,88 +79,43 @@
     <t>Открытый конкурс</t>
   </si>
   <si>
+    <t>Из одного источника по несостоявшимся закупкам не ГЗ</t>
+  </si>
+  <si>
     <t>Запрос ценовых предложений (не ГЗ new)</t>
   </si>
   <si>
-    <t>2025-06-17 17:40:00</t>
-  </si>
-  <si>
-    <t>2025-06-18 08:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-17 16:15:03</t>
-  </si>
-  <si>
-    <t>2025-06-17 16:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-17 15:55:21</t>
-  </si>
-  <si>
-    <t>2025-06-17 12:30:12</t>
-  </si>
-  <si>
-    <t>2025-06-17 11:30:00</t>
-  </si>
-  <si>
-    <t>2025-06-17 11:15:48</t>
-  </si>
-  <si>
-    <t>2025-06-17 10:30:00</t>
-  </si>
-  <si>
-    <t>2025-06-17 09:41:15</t>
-  </si>
-  <si>
-    <t>2025-06-17 08:40:00</t>
-  </si>
-  <si>
-    <t>2025-06-17 09:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 18:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 17:20:00</t>
-  </si>
-  <si>
-    <t>2025-06-24 09:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 14:50:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 16:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 14:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 10:08:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 10:10:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 10:20:36</t>
-  </si>
-  <si>
-    <t>2025-06-16 09:43:22</t>
-  </si>
-  <si>
-    <t>2025-06-16 17:55:00</t>
-  </si>
-  <si>
-    <t>2025-06-17 12:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-16 08:28:24</t>
-  </si>
-  <si>
-    <t>2025-06-17 08:00:00</t>
-  </si>
-  <si>
-    <t>2025-06-18 09:00:00</t>
+    <t>2025-08-05 11:06:41</t>
+  </si>
+  <si>
+    <t>2025-08-05 11:30:00</t>
+  </si>
+  <si>
+    <t>2025-08-05 11:49:42</t>
+  </si>
+  <si>
+    <t>2025-08-05 10:10:00</t>
+  </si>
+  <si>
+    <t>2025-08-05 16:00:00</t>
+  </si>
+  <si>
+    <t>2025-08-05 08:00:22</t>
+  </si>
+  <si>
+    <t>2025-08-05 08:00:54</t>
+  </si>
+  <si>
+    <t>2025-08-12 09:00:00</t>
+  </si>
+  <si>
+    <t>2025-08-06 09:07:21</t>
+  </si>
+  <si>
+    <t>2025-08-11 09:00:00</t>
+  </si>
+  <si>
+    <t>2025-08-06 09:00:00</t>
   </si>
   <si>
     <t>клапан</t>
@@ -582,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -604,13 +511,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -618,13 +525,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -632,13 +539,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -646,13 +553,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -660,13 +567,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -674,13 +581,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -688,13 +595,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -702,13 +609,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -716,13 +623,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -730,13 +637,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -744,13 +651,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -758,13 +665,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -772,13 +679,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -786,13 +693,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -800,237 +707,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1050,22 +733,6 @@
     <hyperlink ref="A14" r:id="rId13"/>
     <hyperlink ref="A15" r:id="rId14"/>
     <hyperlink ref="A16" r:id="rId15"/>
-    <hyperlink ref="A17" r:id="rId16"/>
-    <hyperlink ref="A18" r:id="rId17"/>
-    <hyperlink ref="A19" r:id="rId18"/>
-    <hyperlink ref="A20" r:id="rId19"/>
-    <hyperlink ref="A21" r:id="rId20"/>
-    <hyperlink ref="A22" r:id="rId21"/>
-    <hyperlink ref="A23" r:id="rId22"/>
-    <hyperlink ref="A24" r:id="rId23"/>
-    <hyperlink ref="A25" r:id="rId24"/>
-    <hyperlink ref="A26" r:id="rId25"/>
-    <hyperlink ref="A27" r:id="rId26"/>
-    <hyperlink ref="A28" r:id="rId27"/>
-    <hyperlink ref="A29" r:id="rId28"/>
-    <hyperlink ref="A30" r:id="rId29"/>
-    <hyperlink ref="A31" r:id="rId30"/>
-    <hyperlink ref="A32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
